--- a/Templates/Template.xlsx
+++ b/Templates/Template.xlsx
@@ -18,67 +18,67 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t>数式は README を参照</x:t>
+  </x:si>
+  <x:si>
+    <x:t>変化点・TEF組込・欠陥除去効率</x:t>
+  </x:si>
+  <x:si>
+    <x:t>m(t) = a(1 - (1+bt)e^(-bt))</x:t>
+  </x:si>
+  <x:si>
+    <x:t>--change-point / --tef / --fre で追加</x:t>
+  </x:si>
+  <x:si>
+    <x:t>拡張モデル</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ohba (1984) の変曲S字型。ψ→0 で指数型、ψ が大きいほど立ち上がりが遅い</x:t>
+  </x:si>
+  <x:si>
+    <x:t>m(t) = a(1-e^(-bt)) / (1+ψ·e^(-bt)), ψ = e^(lnψ)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>変曲S字型（Ohba）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Goel (1985) の一般化GO。c&gt;1でS字、c=1で指数型、c&lt;1で凸型</x:t>
+  </x:si>
+  <x:si>
     <x:t>m(t) = a(1 - e^(-b·t^c))</x:t>
   </x:si>
   <x:si>
+    <x:t>Goel一般化（Weibull型）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>非対称S字。終盤の収束が急。m(0)=0 に切断・正規化したゴンペルツ曲線</x:t>
+  </x:si>
+  <x:si>
+    <x:t>m(t) = a(e^(-b·e^(-ct)) - e^(-b)) / (1 - e^(-b))</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ゴンペルツ（切断型）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>テスト初期の習熟を考慮</x:t>
+  </x:si>
+  <x:si>
+    <x:t>遅延S字型</x:t>
+  </x:si>
+  <x:si>
+    <x:t>最もシンプル、バグ発見率一定</x:t>
+  </x:si>
+  <x:si>
+    <x:t>基本</x:t>
+  </x:si>
+  <x:si>
+    <x:t>m(t) = a(1 - e^(-bt))</x:t>
+  </x:si>
+  <x:si>
+    <x:t>指数型（Goel-Okumoto）</x:t>
+  </x:si>
+  <x:si>
     <x:t>パラメータb（変化点モデルは b₁）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>数式は README を参照</x:t>
-  </x:si>
-  <x:si>
-    <x:t>変化点・TEF組込・欠陥除去効率</x:t>
-  </x:si>
-  <x:si>
-    <x:t>--change-point / --tef / --fre で追加</x:t>
-  </x:si>
-  <x:si>
-    <x:t>拡張モデル</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ohba (1984) の変曲S字型。ψ=0 で指数型、ψ が大きいほど立ち上がりが遅い</x:t>
-  </x:si>
-  <x:si>
-    <x:t>m(t) = a(1-e^(-bt)) / (1+ψ·e^(-bt))</x:t>
-  </x:si>
-  <x:si>
-    <x:t>変曲S字型（Ohba）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Goel (1985) の一般化GO。c&gt;1でS字、c=1で指数型、c&lt;1で凸型</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Goel一般化（Weibull型）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>非対称S字。終盤の収束が急。m(0)=0 に切断・正規化したゴンペルツ曲線</x:t>
-  </x:si>
-  <x:si>
-    <x:t>m(t) = a(e^(-b·e^(-ct)) - e^(-b)) / (1 - e^(-b))</x:t>
-  </x:si>
-  <x:si>
-    <x:t>m(t) = a(1 - e^(-bt))</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ゴンペルツ（切断型）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>テスト初期の習熟を考慮</x:t>
-  </x:si>
-  <x:si>
-    <x:t>m(t) = a(1 - (1+bt)e^(-bt))</x:t>
-  </x:si>
-  <x:si>
-    <x:t>遅延S字型</x:t>
-  </x:si>
-  <x:si>
-    <x:t>最もシンプル、バグ発見率一定</x:t>
-  </x:si>
-  <x:si>
-    <x:t>基本</x:t>
-  </x:si>
-  <x:si>
-    <x:t>指数型（Goel-Okumoto）</x:t>
   </x:si>
   <x:si>
     <x:t>その他のパラメータ</x:t>
@@ -636,7 +636,7 @@
     <x:pageSetUpPr/>
   </x:sheetPr>
   <x:dimension ref="A1:U24"/>
-  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.090625" defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.210625" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="25" style="0" customWidth="1"/>
     <x:col min="2" max="21" width="8" style="0" customWidth="1"/>
@@ -1113,7 +1113,7 @@
     <x:pageSetUpPr/>
   </x:sheetPr>
   <x:dimension ref="A1:D27"/>
-  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.090625" defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.210625" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="25" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="35" style="0" customWidth="1"/>
@@ -1159,41 +1159,41 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>11</x:v>
@@ -1204,41 +1204,41 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
@@ -1262,7 +1262,7 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
